--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0106.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0106.xlsx
@@ -5709,7 +5709,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Cậu thấy người nhảy rào thuần hóa Ironhoof không? {Male=Anh ta;Female=Cô ấy} ngầu thật đấy…</t>
+          <t>Cậu thấy người nhảy rào thuần hóa Ironhoof không? {Male=He's;Female=She's} ngầu thật đấy…</t>
         </is>
       </c>
     </row>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>"Ta đã thấy cậu lao vào hàng rào không chút do dự, chỉ để giúp mọi người và cứu Ironhoof. Không phải ai cũng làm được như vậy đâu. Cảm ơn nhé," Dhalifa nói!</t>
+          <t>"Tao đã thấy cậu lao vào hàng rào không chút do dự, chỉ để giúp mọi người và cứu Ironhoof. Không phải ai cũng làm được như vậy đâu. Cảm ơn nhé," Dhalifa nói!</t>
         </is>
       </c>
     </row>
@@ -6684,7 +6684,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Ta. Chỉ có ta. Sống sót.</t>
+          <t>Tao. Chỉ có tao. Sống sót.</t>
         </is>
       </c>
     </row>
@@ -7009,7 +7009,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Talkie... Ở Học viện. Nó đã chăm sóc ta.</t>
+          <t>Talkie... Ở Học viện. Nó đã chăm sóc tao.</t>
         </is>
       </c>
     </row>
@@ -10779,7 +10779,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Ta không quan tâm ngươi nói gì về chúng ta, nhưng phá hoại thiết bị của chúng ta? Ngươi đã vượt quá giới hạn rồi! Ngươi sẽ không thoát được mà không chịu trách nhiệm đâu!</t>
+          <t>Tao không quan tâm mày nói gì về chúng tao, nhưng phá hoại thiết bị của chúng tao? Mày đã vượt quá giới hạn rồi! Mày sẽ không thoát được mà không chịu trách nhiệm đâu!</t>
         </is>
       </c>
     </row>
@@ -11104,7 +11104,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Ta cứ nghĩ cậu sẽ quay lại sau vụ đó, nhưng cậu không về... Và nếu họ xây dựng lại xong, cậu sẽ chẳng bao giờ rời đi nữa!</t>
+          <t>Tao cứ nghĩ cậu sẽ quay lại sau vụ đó, nhưng cậu không về... Và nếu họ xây dựng lại xong, cậu sẽ chẳng bao giờ rời đi nữa!</t>
         </is>
       </c>
     </row>
@@ -13704,7 +13704,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Ta. Chỉ có ta. Sống sót.</t>
+          <t>Tao. Chỉ có tao. Sống sót.</t>
         </is>
       </c>
     </row>
@@ -14029,7 +14029,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Talkie... Ở Học viện. Nó đã chăm sóc ta.</t>
+          <t>Talkie... Ở Học viện. Nó đã chăm sóc tao.</t>
         </is>
       </c>
     </row>
@@ -16824,7 +16824,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Tất nhiên rồi.</t>
+          <t>Đương nhiên.</t>
         </is>
       </c>
     </row>
@@ -16889,7 +16889,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Vậy… chắc cậu cũng biết hầu hết người Roya sống ở Rừng Bjartr phải không? Nhưng bộ tộc của mình thỉnh thoảng vẫn đến nơi này.</t>
+          <t>Vậy… chắc cậu cũng biết hầu hết người Roya sống ở Bjartr Woods phải không? Nhưng bộ tộc của mình thỉnh thoảng vẫn đến nơi này.</t>
         </is>
       </c>
     </row>
@@ -16954,7 +16954,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Ngày Bão Hư Không ập đến, bố mẹ ta đã đến đây cùng nhóm của họ để gặp ta.</t>
+          <t>Ngày Bão Hư Không ập đến, bố mẹ tao đã đến đây cùng nhóm của họ để gặp tao.</t>
         </is>
       </c>
     </row>
@@ -17279,7 +17279,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Người lớn sẽ hoảng loạn la hét, còn ta thì chỉ việc ngồi trên đầu Ironhoof mà vỗ tay.</t>
+          <t>Người lớn sẽ hoảng loạn la hét, còn tao thì chỉ việc ngồi trên đầu Ironhoof mà vỗ tay.</t>
         </is>
       </c>
     </row>
@@ -17474,7 +17474,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Ta đang nghĩ, phải chăng vì dạo này ta cứ ở gần bọn họ? Có thể vẫn còn chút năng lượng Bão Hư Không sót lại trong người ta, và ta—</t>
+          <t>Tao đang nghĩ, phải chăng vì dạo này tao cứ ở gần bọn họ? Có thể vẫn còn chút năng lượng Bão Hư Không sót lại trong người tao, và tao—</t>
         </is>
       </c>
     </row>
@@ -17994,7 +17994,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Những kẻ bị ruồng bỏ nào? Ta đâu có thấy ai ở gần đây! Talkie! Lại đây dịch giùm ta!</t>
+          <t>Những kẻ bị ruồng bỏ nào? Tao đâu có thấy ai ở gần đây! Talkie! Lại đây dịch giùm tao!</t>
         </is>
       </c>
     </row>
@@ -18579,7 +18579,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Ta nghe nói cậu đã đi qua bao nhiêu nơi rồi. Cơ hội được thấy, được học bao điều mới... Hừm, chắc là tuyệt lắm nhỉ.</t>
+          <t>Tao nghe nói cậu đã đi qua bao nhiêu nơi rồi. Cơ hội được thấy, được học bao điều mới... Hừm, chắc là tuyệt lắm nhỉ.</t>
         </is>
       </c>
     </row>
@@ -22479,7 +22479,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Còn nữa… ta thật sự hối hận về những gì mình đã làm.</t>
+          <t>Còn nữa… tao thật sự hối hận về những gì mình đã làm.</t>
         </is>
       </c>
     </row>
@@ -22544,7 +22544,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Ta đã phải trải qua bao nhiêu khó khăn để giành được lòng tin của Soliskin và trở thành Shepherdess, vậy mà giờ nhìn ta này… Thở dài. Ta sẽ làm mọi thứ để sửa chữa sai lầm.</t>
+          <t>Tao đã phải trải qua bao nhiêu khó khăn để giành được lòng tin của Soliskin và trở thành Shepherdess, vậy mà giờ nhìn tao này… Thở dài. Tao sẽ làm mọi thứ để sửa chữa sai lầm.</t>
         </is>
       </c>
     </row>
@@ -23714,7 +23714,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Giờ sao đây, Sephira? Lại trông chờ người khác dọn dẹp đống hỗn độn của cậu à?</t>
+          <t>Giờ sao đây, Sephira? Lại trông chờ người khác dọn dẹp đống hỗn độn của mày à?</t>
         </is>
       </c>
     </row>
@@ -25989,7 +25989,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Được thôi. Cảnh từ Cầu Spacetrek–Bjartr đẹp tuyệt, và nó sẽ đưa chúng ta thẳng về Rừng Bjartr luôn.</t>
+          <t>Được thôi. Cảnh từ Cầu Spacetrek–Bjartr đẹp tuyệt, và nó sẽ đưa chúng ta thẳng về Bjartr Woods luôn.</t>
         </is>
       </c>
     </row>
@@ -28979,7 +28979,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Ừ, ta nhớ. Hồi đó, cô ấy...</t>
+          <t>Ừ, tao nhớ. Hồi đó, cô ấy...</t>
         </is>
       </c>
     </row>
@@ -29889,7 +29889,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Phục kích à? Đừng có mà ảo tưởng. Ta nghe {PlayerName} đã dạy cho lũ ngươi một bài học đích đáng rồi. Chúng nó đến giúp ngươi? Đừng mơ!</t>
+          <t>Phục kích à? Đừng có mà ảo tưởng. Tao nghe {PlayerName} đã dạy cho lũ mày một bài học đích đáng rồi. Chúng nó đến giúp mày? Đừng mơ!</t>
         </is>
       </c>
     </row>
@@ -29954,7 +29954,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Đồ khốn, Sephira! Ngươi cũng từng là một trong chúng ta mà!</t>
+          <t>Đồ khốn, Sephira! Mày cũng từng là một trong chúng tao mà!</t>
         </is>
       </c>
     </row>
@@ -30019,7 +30019,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Giờ thì ngươi lủi về làng, được tha thứ, rồi lại ra vẻ ta đây hơn người à? Ghê tởm!</t>
+          <t>Giờ thì mày lủi về làng, được tha thứ, rồi lại ra vẻ ta đây hơn người à? Ghê tởm!</t>
         </is>
       </c>
     </row>
@@ -31189,7 +31189,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Ta bảo không! Sinh nhật ư... Làm sao ta có thể ăn mừng được nữa...</t>
+          <t>Tao bảo không! Sinh nhật ư... Làm sao tao có thể ăn mừng được nữa...</t>
         </is>
       </c>
     </row>
